--- a/Sedes_a_priorizar_Zona_Norte.xlsx
+++ b/Sedes_a_priorizar_Zona_Norte.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>49.83723646551724</v>
+        <v>49.82811362068965</v>
       </c>
     </row>
     <row r="4">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>52.15077267241379</v>
+        <v>52.14164982758621</v>
       </c>
     </row>
     <row r="8">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>52.8899275</v>
+        <v>52.88080465517241</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>53.98524112068966</v>
+        <v>53.97611827586207</v>
       </c>
     </row>
   </sheetData>
